--- a/data/trans_camb/P1435_2011_2023-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1435_2011_2023-Edad-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,42</t>
+          <t>3,33</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>2,1</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 5,25</t>
+          <t>0,0; 5,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 8,17</t>
+          <t>0,65; 7,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,98</t>
+          <t>0,5; 4,52</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>581,55%</t>
+          <t>506,58%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>206,67%</t>
+          <t>201,42%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>231,43%</t>
+          <t>230,55%</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 845,97</t>
+          <t>5,36; 803,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,14; 843,07</t>
+          <t>25,18; 798,75</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>2,19</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>1,52</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,65</t>
+          <t>-0,14; 2,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,04</t>
+          <t>0,03; 4,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,96</t>
+          <t>0,2; 2,82</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>308,46%</t>
+          <t>230,64%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111,57%</t>
+          <t>117,38%</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 259,04</t>
+          <t>-8,18; 281,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 320,56</t>
+          <t>4,62; 317,11</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,48</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,23</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,47</t>
+          <t>0,38; 2,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,49</t>
+          <t>1,36; 5,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,62</t>
+          <t>1,26; 3,43</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>122,04%</t>
+          <t>119,45%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159,05%</t>
+          <t>153,31%</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,64; 274,86</t>
+          <t>32,33; 279,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52,03; 377,37</t>
+          <t>57,13; 344,16</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>3,34</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>2,58</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,46</t>
+          <t>0,37; 3,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,7</t>
+          <t>0,48; 5,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,66</t>
+          <t>1,05; 4,02</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>166,07%</t>
+          <t>255,33%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>78,11%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,1; 908,42</t>
+          <t>-0,66; 1193,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,27; 147,99</t>
+          <t>4,07; 126,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 145,43</t>
+          <t>23,84; 159,72</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>7,78</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>4,37</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,28</t>
+          <t>-0,23; 2,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,49; 10,74</t>
+          <t>3,93; 10,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,88</t>
+          <t>2,51; 6,27</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>138,84%</t>
+          <t>154,84%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>104,14%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>104,66%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 863,75</t>
+          <t>-33,17; 930,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>36,26; 209,58</t>
+          <t>37,07; 196,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32,69; 189,83</t>
+          <t>45,59; 205,31</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>38,33</t>
+          <t>9,01</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>5,91</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,43</t>
+          <t>1,43; 4,21</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7,55; 73,55</t>
+          <t>6,16; 11,79</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,12; 60,96</t>
+          <t>4,24; 7,59</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1247,79%</t>
+          <t>293,38%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1537,87%</t>
+          <t>360,93%</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>212,49; 5914,3</t>
+          <t>126,06; 685,54</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>272,4; 10001,35</t>
+          <t>136,93; 722,16</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>7,59</t>
+          <t>7,71</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>5,09</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,6</t>
+          <t>-0,34; 2,68</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5,42; 9,83</t>
+          <t>5,57; 10,08</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,77; 6,61</t>
+          <t>3,73; 6,67</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>293,18%</t>
+          <t>274,44%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>865,94%</t>
+          <t>880,46%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>722,17%</t>
+          <t>727,24%</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>238,26; 3362,11</t>
+          <t>233,38; 3378,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>205,99; 3322,51</t>
+          <t>251,05; 3243,63</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>10,32</t>
+          <t>5,39</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5,96</t>
+          <t>3,45</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,9</t>
+          <t>0,91; 1,92</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,86; 24,8</t>
+          <t>4,37; 6,36</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3,0; 17,11</t>
+          <t>2,85; 3,98</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>409,18%</t>
+          <t>425,09%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>289,8%</t>
+          <t>151,26%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>302,16%</t>
+          <t>174,73%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>163,09; 989,44</t>
+          <t>182,39; 1032,7</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>129,51; 814,61</t>
+          <t>109,87; 209,28</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>146,87; 943,83</t>
+          <t>126,28; 232,74</t>
         </is>
       </c>
     </row>
